--- a/artfynd/A 7085-2024 artfynd.xlsx
+++ b/artfynd/A 7085-2024 artfynd.xlsx
@@ -6055,7 +6055,7 @@
         <v>115265477</v>
       </c>
       <c r="B50" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 7085-2024 artfynd.xlsx
+++ b/artfynd/A 7085-2024 artfynd.xlsx
@@ -6055,7 +6055,7 @@
         <v>115265477</v>
       </c>
       <c r="B50" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 7085-2024 artfynd.xlsx
+++ b/artfynd/A 7085-2024 artfynd.xlsx
@@ -6165,7 +6165,7 @@
         <v>123536435</v>
       </c>
       <c r="B51" t="n">
-        <v>90986</v>
+        <v>91003</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>123536478</v>
       </c>
       <c r="B52" t="n">
-        <v>90986</v>
+        <v>91003</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 7085-2024 artfynd.xlsx
+++ b/artfynd/A 7085-2024 artfynd.xlsx
@@ -6162,10 +6162,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123536435</v>
+        <v>123536478</v>
       </c>
       <c r="B51" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6209,10 +6209,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571486</v>
+        <v>571500</v>
       </c>
       <c r="R51" t="n">
-        <v>6461662</v>
+        <v>6461643</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6272,10 +6272,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123536478</v>
+        <v>123536435</v>
       </c>
       <c r="B52" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571500</v>
+        <v>571486</v>
       </c>
       <c r="R52" t="n">
-        <v>6461643</v>
+        <v>6461662</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>

--- a/artfynd/A 7085-2024 artfynd.xlsx
+++ b/artfynd/A 7085-2024 artfynd.xlsx
@@ -6165,7 +6165,7 @@
         <v>123536478</v>
       </c>
       <c r="B51" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>123536435</v>
       </c>
       <c r="B52" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 7085-2024 artfynd.xlsx
+++ b/artfynd/A 7085-2024 artfynd.xlsx
@@ -6162,7 +6162,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123536478</v>
+        <v>123536435</v>
       </c>
       <c r="B51" t="n">
         <v>91010</v>
@@ -6209,10 +6209,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571500</v>
+        <v>571486</v>
       </c>
       <c r="R51" t="n">
-        <v>6461643</v>
+        <v>6461662</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6272,7 +6272,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123536435</v>
+        <v>123536478</v>
       </c>
       <c r="B52" t="n">
         <v>91010</v>
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571486</v>
+        <v>571500</v>
       </c>
       <c r="R52" t="n">
-        <v>6461662</v>
+        <v>6461643</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>

--- a/artfynd/A 7085-2024 artfynd.xlsx
+++ b/artfynd/A 7085-2024 artfynd.xlsx
@@ -6162,7 +6162,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123536435</v>
+        <v>123536478</v>
       </c>
       <c r="B51" t="n">
         <v>91010</v>
@@ -6209,10 +6209,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571486</v>
+        <v>571500</v>
       </c>
       <c r="R51" t="n">
-        <v>6461662</v>
+        <v>6461643</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6272,7 +6272,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123536478</v>
+        <v>123536435</v>
       </c>
       <c r="B52" t="n">
         <v>91010</v>
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571500</v>
+        <v>571486</v>
       </c>
       <c r="R52" t="n">
-        <v>6461643</v>
+        <v>6461662</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>

--- a/artfynd/A 7085-2024 artfynd.xlsx
+++ b/artfynd/A 7085-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115036955</v>
+        <v>115265361</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mars-170, Ög</t>
+          <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571760</v>
+        <v>571610</v>
       </c>
       <c r="R2" t="n">
-        <v>6461576</v>
+        <v>6461799</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,27 +764,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas Lindebring</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Lindebring</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115265562</v>
+        <v>115265442</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,31 +787,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +814,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571536</v>
+        <v>571508</v>
       </c>
       <c r="R3" t="n">
-        <v>6461550</v>
+        <v>6461644</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +858,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115265406</v>
+        <v>115958173</v>
       </c>
       <c r="B4" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,44 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mossarp, Ög</t>
+          <t>Mossarp, Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571502</v>
+        <v>571451</v>
       </c>
       <c r="R4" t="n">
-        <v>6461662</v>
+        <v>6461661</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,12 +942,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,76 +966,66 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115265315</v>
+        <v>115958869</v>
       </c>
       <c r="B5" t="n">
-        <v>96331</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2604</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mossarp , Ög</t>
+          <t>Mossarp, Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571622</v>
+        <v>571482</v>
       </c>
       <c r="R5" t="n">
-        <v>6461787</v>
+        <v>6461653</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,12 +1049,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,34 +1073,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115265487</v>
+        <v>116031932</v>
       </c>
       <c r="B6" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,40 +1102,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2064</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571442</v>
+        <v>571448</v>
       </c>
       <c r="R6" t="n">
-        <v>6461563</v>
+        <v>6461671</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,12 +1156,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,34 +1170,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115265361</v>
+        <v>116031933</v>
       </c>
       <c r="B7" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,22 +1217,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571610</v>
+        <v>571597</v>
       </c>
       <c r="R7" t="n">
-        <v>6461799</v>
+        <v>6461688</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,12 +1253,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,34 +1267,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115265362</v>
+        <v>116031918</v>
       </c>
       <c r="B8" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75379</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1345,40 +1296,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1118</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571610</v>
+        <v>571582</v>
       </c>
       <c r="R8" t="n">
-        <v>6461799</v>
+        <v>6461534</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,12 +1350,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På väldigt liten, väldigt senvuxen ek.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,72 +1369,69 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115510856</v>
+        <v>115265575</v>
       </c>
       <c r="B9" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571830</v>
+        <v>571660</v>
       </c>
       <c r="R9" t="n">
-        <v>6461594</v>
+        <v>6461629</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,90 +1463,73 @@
           <t>2024-03-16</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115533037</v>
+        <v>115955738</v>
       </c>
       <c r="B10" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>sluttningen, Yxnerums kyrka, Ög</t>
+          <t>Mossarp, Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571512</v>
+        <v>571649</v>
       </c>
       <c r="R10" t="n">
-        <v>6461549</v>
+        <v>6461616</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1620,27 +1553,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>spillkråke hack</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,27 +1583,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115510866</v>
+        <v>115955896</v>
       </c>
       <c r="B11" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,37 +1606,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mossarp, Ög</t>
+          <t>Mossarp, Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571714</v>
+        <v>571653</v>
       </c>
       <c r="R11" t="n">
-        <v>6461595</v>
+        <v>6461627</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,12 +1669,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,31 +1695,36 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115532590</v>
+        <v>116031934</v>
       </c>
       <c r="B12" t="n">
-        <v>96612</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,42 +1732,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224363</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla höjden, Yxnerums kyrka, Ög</t>
+          <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571624</v>
+        <v>571648</v>
       </c>
       <c r="R12" t="n">
-        <v>6461510</v>
+        <v>6461618</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,22 +1786,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ca 20 st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,72 +1805,69 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115510857</v>
+        <v>115265487</v>
       </c>
       <c r="B13" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92289</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>2064</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571762</v>
+        <v>571442</v>
       </c>
       <c r="R13" t="n">
-        <v>6461583</v>
+        <v>6461563</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,79 +1899,70 @@
           <t>2024-03-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ca 50 m2</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115510854</v>
+        <v>115959970</v>
       </c>
       <c r="B14" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92289</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2064</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mossarp, Ög</t>
+          <t>Mossarp, Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571453</v>
+        <v>571559</v>
       </c>
       <c r="R14" t="n">
-        <v>6461572</v>
+        <v>6461525</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,17 +1989,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>På gammal klen, nedbruten tallåga. Udda växtplats, på gränsen till plantaget.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,62 +2024,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115955366</v>
+        <v>116031919</v>
       </c>
       <c r="B15" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92289</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>2064</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mossarp (Mossarp), Ög</t>
+          <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571795</v>
+        <v>571582</v>
       </c>
       <c r="R15" t="n">
-        <v>6461628</v>
+        <v>6461534</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,22 +2101,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2204,73 +2121,61 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115956030</v>
+        <v>115265315</v>
       </c>
       <c r="B16" t="n">
-        <v>90943</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97811</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5454</v>
+        <v>2604</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mossarp (Mossarp), Ög</t>
+          <t>Mossarp , Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>571653</v>
+        <v>571622</v>
       </c>
       <c r="R16" t="n">
-        <v>6461627</v>
+        <v>6461787</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2297,22 +2202,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,88 +2220,67 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115955880</v>
+        <v>115265541</v>
       </c>
       <c r="B17" t="n">
-        <v>90943</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97811</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5454</v>
+        <v>2604</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mossarp (Mossarp), Ög</t>
+          <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571639</v>
+        <v>571478</v>
       </c>
       <c r="R17" t="n">
-        <v>6461613</v>
+        <v>6461539</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,22 +2304,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,18 +2318,19 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2475,12 +2340,7 @@
         <v>115956400</v>
       </c>
       <c r="B18" t="n">
-        <v>96331</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,7 +2368,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mossarp (Mossarp), Ög</t>
+          <t>Mossarp, Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -2584,15 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115955386</v>
+        <v>116031929</v>
       </c>
       <c r="B19" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97811</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2600,53 +2455,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>2604</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571826</v>
+        <v>571604</v>
       </c>
       <c r="R19" t="n">
-        <v>6461630</v>
+        <v>6461669</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2670,22 +2509,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,34 +2528,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115955282</v>
+        <v>115265447</v>
       </c>
       <c r="B20" t="n">
-        <v>103146</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,38 +2557,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222412</v>
+        <v>2606</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2769,13 +2585,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571855</v>
+        <v>571505</v>
       </c>
       <c r="R20" t="n">
-        <v>6461638</v>
+        <v>6461624</v>
       </c>
       <c r="S20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2799,22 +2615,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,90 +2633,70 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Bland annat asp och tall omkring. En bäck ca 10 m nedanför.</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115956539</v>
+        <v>115265406</v>
       </c>
       <c r="B21" t="n">
-        <v>96331</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2604</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mossarp (Mossarp), Ög</t>
+          <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>571598</v>
+        <v>571502</v>
       </c>
       <c r="R21" t="n">
-        <v>6461679</v>
+        <v>6461662</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2934,22 +2720,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2962,95 +2738,60 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Talldominerad skog med lövinslag, främst asp och ek. Betespåverkas skog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Leuciscus aspius</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Leuciscus aspius</t>
-        </is>
-      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115955703</v>
+        <v>116031913</v>
       </c>
       <c r="B22" t="n">
-        <v>96822</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220250</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mossarp (Mossarp), Ög</t>
+          <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>571795</v>
+        <v>571488</v>
       </c>
       <c r="R22" t="n">
-        <v>6461628</v>
+        <v>6461658</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3077,22 +2818,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3107,27 +2838,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115959970</v>
+        <v>123536289</v>
       </c>
       <c r="B23" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3135,37 +2861,44 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2064</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>A.David</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mossarp (Mossarp), Ög</t>
+          <t>Östantorp, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571559</v>
+        <v>571462</v>
       </c>
       <c r="R23" t="n">
-        <v>6461525</v>
+        <v>6461671</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3189,27 +2922,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gammal klen, nedbruten tallåga. Udda växtplats, på gränsen till plantaget.</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3218,33 +2936,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115956782</v>
+        <v>123536435</v>
       </c>
       <c r="B24" t="n">
-        <v>90943</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,37 +2966,44 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5454</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mossarp (Mossarp), Ög</t>
+          <t>Östantorp, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571599</v>
+        <v>571486</v>
       </c>
       <c r="R24" t="n">
-        <v>6461686</v>
+        <v>6461662</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3306,22 +3027,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3330,33 +3041,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115958869</v>
+        <v>123536478</v>
       </c>
       <c r="B25" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,37 +3071,44 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mossarp (Mossarp), Ög</t>
+          <t>Östantorp, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571482</v>
+        <v>571500</v>
       </c>
       <c r="R25" t="n">
-        <v>6461653</v>
+        <v>6461643</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3418,22 +3132,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3442,68 +3146,64 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115957068</v>
+        <v>115955880</v>
       </c>
       <c r="B26" t="n">
-        <v>89736</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5685</v>
+        <v>5454</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mossarp (Mossarp), Ög</t>
+          <t>Mossarp, Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571575</v>
+        <v>571639</v>
       </c>
       <c r="R26" t="n">
-        <v>6461677</v>
+        <v>6461613</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3535,7 +3235,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3545,7 +3245,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3572,53 +3272,59 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115955738</v>
+        <v>115956030</v>
       </c>
       <c r="B27" t="n">
-        <v>90951</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1339</v>
+        <v>5454</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mossarp (Mossarp), Ög</t>
+          <t>Mossarp, Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571649</v>
+        <v>571653</v>
       </c>
       <c r="R27" t="n">
-        <v>6461616</v>
+        <v>6461627</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3647,7 +3353,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3657,7 +3363,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3666,33 +3372,49 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115956071</v>
+        <v>115956782</v>
       </c>
       <c r="B28" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,34 +3422,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5454</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mossarp (Mossarp), Ög</t>
+          <t>Mossarp, Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571639</v>
+        <v>571599</v>
       </c>
       <c r="R28" t="n">
-        <v>6461613</v>
+        <v>6461686</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3759,7 +3481,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3769,7 +3491,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3796,15 +3518,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115956167</v>
+        <v>115957098</v>
       </c>
       <c r="B29" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,48 +3529,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5454</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mossarp (Mossarp), Ög</t>
+          <t>Mossarp, Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571613</v>
+        <v>571578</v>
       </c>
       <c r="R29" t="n">
-        <v>6461617</v>
+        <v>6461698</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3882,7 +3588,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3892,7 +3598,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3901,101 +3607,66 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115955896</v>
+        <v>116031923</v>
       </c>
       <c r="B30" t="n">
-        <v>90951</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1339</v>
+        <v>5454</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mossarp (Mossarp), Ög</t>
+          <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571653</v>
+        <v>571601</v>
       </c>
       <c r="R30" t="n">
-        <v>6461627</v>
+        <v>6461700</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4019,22 +3690,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:46</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4045,63 +3706,48 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>116031929</v>
+        <v>116031924</v>
       </c>
       <c r="B31" t="n">
-        <v>96340</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2604</v>
+        <v>5454</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4111,10 +3757,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571604</v>
+        <v>571654</v>
       </c>
       <c r="R31" t="n">
-        <v>6461669</v>
+        <v>6461605</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4147,11 +3793,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4178,37 +3819,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>116031937</v>
+        <v>116031926</v>
       </c>
       <c r="B32" t="n">
-        <v>99918</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>5454</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4218,10 +3854,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571626</v>
+        <v>571583</v>
       </c>
       <c r="R32" t="n">
-        <v>6461614</v>
+        <v>6461674</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4280,50 +3916,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>116031918</v>
+        <v>115957068</v>
       </c>
       <c r="B33" t="n">
-        <v>74536</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1118</v>
+        <v>5685</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mossarp, Ög</t>
+          <t>Mossarp, Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571582</v>
+        <v>571575</v>
       </c>
       <c r="R33" t="n">
-        <v>6461534</v>
+        <v>6461677</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4350,17 +3981,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På väldigt liten, väldigt senvuxen ek.</t>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4375,12 +4011,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4390,12 +4026,7 @@
         <v>116031928</v>
       </c>
       <c r="B34" t="n">
-        <v>89745</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4489,53 +4120,51 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>116031939</v>
+        <v>115265362</v>
       </c>
       <c r="B35" t="n">
-        <v>99918</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571780</v>
+        <v>571610</v>
       </c>
       <c r="R35" t="n">
-        <v>6461622</v>
+        <v>6461799</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4559,12 +4188,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4573,71 +4202,70 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>116031915</v>
+        <v>115265437</v>
       </c>
       <c r="B36" t="n">
-        <v>96831</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220250</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571666</v>
+        <v>571500</v>
       </c>
       <c r="R36" t="n">
-        <v>6461627</v>
+        <v>6461649</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4661,12 +4289,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4675,18 +4303,19 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4696,12 +4325,7 @@
         <v>116031909</v>
       </c>
       <c r="B37" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4795,37 +4419,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>116031936</v>
+        <v>116031910</v>
       </c>
       <c r="B38" t="n">
-        <v>99918</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4835,10 +4454,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571807</v>
+        <v>571614</v>
       </c>
       <c r="R38" t="n">
-        <v>6461626</v>
+        <v>6461629</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4871,6 +4490,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4897,15 +4521,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>116031940</v>
+        <v>115265369</v>
       </c>
       <c r="B39" t="n">
-        <v>99918</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4913,37 +4532,53 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571630</v>
+        <v>571571</v>
       </c>
       <c r="R39" t="n">
-        <v>6461644</v>
+        <v>6461688</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4967,12 +4602,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4987,65 +4622,68 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>116031913</v>
+        <v>115265477</v>
       </c>
       <c r="B40" t="n">
-        <v>90361</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571488</v>
+        <v>571518</v>
       </c>
       <c r="R40" t="n">
-        <v>6461658</v>
+        <v>6461594</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5069,12 +4707,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5089,65 +4727,68 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>116031910</v>
+        <v>115265502</v>
       </c>
       <c r="B41" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571614</v>
+        <v>571465</v>
       </c>
       <c r="R41" t="n">
-        <v>6461629</v>
+        <v>6461543</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5171,17 +4812,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5196,65 +4832,68 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>116031924</v>
+        <v>115265562</v>
       </c>
       <c r="B42" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5454</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571654</v>
+        <v>571536</v>
       </c>
       <c r="R42" t="n">
-        <v>6461605</v>
+        <v>6461550</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5278,12 +4917,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5298,27 +4937,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>116031911</v>
+        <v>115510854</v>
       </c>
       <c r="B43" t="n">
-        <v>103155</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5326,21 +4960,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5350,10 +4984,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571833</v>
+        <v>571453</v>
       </c>
       <c r="R43" t="n">
-        <v>6461635</v>
+        <v>6461572</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5380,17 +5014,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt spridd i området.</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5417,15 +5051,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>116031934</v>
+        <v>115510856</v>
       </c>
       <c r="B44" t="n">
-        <v>90960</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5433,21 +5062,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5457,10 +5086,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571648</v>
+        <v>571830</v>
       </c>
       <c r="R44" t="n">
-        <v>6461618</v>
+        <v>6461594</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5487,17 +5116,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ca 20 st</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5524,19 +5153,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>116031916</v>
+        <v>115533037</v>
       </c>
       <c r="B45" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5557,28 +5181,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mossarp, Ög</t>
+          <t>sluttningen, Yxnerums kyrka, Ög</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>571702</v>
+        <v>571512</v>
       </c>
       <c r="R45" t="n">
-        <v>6461582</v>
+        <v>6461549</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5602,17 +5226,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>spillkråke hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5627,62 +5261,65 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>116031919</v>
+        <v>116031916</v>
       </c>
       <c r="B46" t="n">
-        <v>90691</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2064</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>571582</v>
+        <v>571702</v>
       </c>
       <c r="R46" t="n">
-        <v>6461534</v>
+        <v>6461582</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5715,6 +5352,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5741,50 +5383,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>116031926</v>
+        <v>116031917</v>
       </c>
       <c r="B47" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5454</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>571583</v>
+        <v>571540</v>
       </c>
       <c r="R47" t="n">
-        <v>6461674</v>
+        <v>6461687</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5817,6 +5462,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färskt bohål.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5843,15 +5493,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>116031912</v>
+        <v>115958200</v>
       </c>
       <c r="B48" t="n">
-        <v>103155</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5859,34 +5504,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222412</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mossarp, Ög</t>
+          <t>Mossarp, Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>571849</v>
+        <v>571451</v>
       </c>
       <c r="R48" t="n">
-        <v>6461631</v>
+        <v>6461646</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5913,17 +5558,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Rikligt spridd i området.</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5938,62 +5593,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>116031933</v>
+        <v>115955703</v>
       </c>
       <c r="B49" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>220250</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mossarp, Ög</t>
+          <t>Mossarp, Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>571597</v>
+        <v>571795</v>
       </c>
       <c r="R49" t="n">
-        <v>6461688</v>
+        <v>6461628</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6020,12 +5670,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6040,73 +5700,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Karin Wilhelmsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>115265477</v>
+        <v>116031915</v>
       </c>
       <c r="B50" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220250</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>besöker bebott bo</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>571518</v>
+        <v>571666</v>
       </c>
       <c r="R50" t="n">
-        <v>6461594</v>
+        <v>6461627</v>
       </c>
       <c r="S50" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6130,12 +5777,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6150,69 +5797,69 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123536478</v>
+        <v>115036955</v>
       </c>
       <c r="B51" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Östantorp, Ög</t>
+          <t>Mars-170, Ög</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>571500</v>
+        <v>571760</v>
       </c>
       <c r="R51" t="n">
-        <v>6461643</v>
+        <v>6461576</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6239,12 +5886,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6260,72 +5907,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Jonas Lindebring</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Jonas Lindebring</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123536435</v>
+        <v>115510857</v>
       </c>
       <c r="B52" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Östantorp, Ög</t>
+          <t>Mossarp, Ög</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>571486</v>
+        <v>571762</v>
       </c>
       <c r="R52" t="n">
-        <v>6461662</v>
+        <v>6461583</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6349,12 +5984,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>ca 50 m2</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6363,22 +6003,1288 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Karin Wilhelmsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>115955282</v>
+      </c>
+      <c r="B53" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Mossarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>571855</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6461638</v>
+      </c>
+      <c r="S53" t="n">
+        <v>26</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Bland annat asp och tall omkring. En bäck ca 10 m nedanför.</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>116031911</v>
+      </c>
+      <c r="B54" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Mossarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>571833</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6461635</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt spridd i området.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>116031912</v>
+      </c>
+      <c r="B55" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Mossarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>571849</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6461631</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt spridd i området.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>115510866</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Mossarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>571714</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6461595</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>115955366</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Mossarp, Mossarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>571795</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6461628</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Malin Gröndahl Maass</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Malin Gröndahl Maass</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>115955386</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Mossarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>571826</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6461630</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>116031936</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Mossarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>571807</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6461626</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>116031937</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Mossarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>571626</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6461614</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>116031938</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Mossarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>571700</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6461611</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>116031939</v>
+      </c>
+      <c r="B62" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Mossarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>571780</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6461622</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>116031940</v>
+      </c>
+      <c r="B63" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Mossarp, Ög</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>571630</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6461644</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Karin Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>115532590</v>
+      </c>
+      <c r="B64" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lilla höjden, Yxnerums kyrka, Ög</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>571624</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6461510</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Yxnerum</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-03-16</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Carina Faxén</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Carina Faxén</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7085-2024 artfynd.xlsx
+++ b/artfynd/A 7085-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031918</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115265575</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115955738</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115955896</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031934</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115265487</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115959970</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031919</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,6 +1667,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115265541</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115265447</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1831,6 +1886,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115955880</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1970,6 +2030,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115956030</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2067,6 +2132,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031924</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2164,6 +2234,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031909</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2266,6 +2341,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031910</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2371,6 +2451,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115265477</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2476,6 +2561,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115265502</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2581,6 +2671,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115265562</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2683,6 +2778,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510854</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2785,6 +2885,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510856</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2905,6 +3010,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115533037</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3015,6 +3125,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031916</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3122,6 +3237,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115955703</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3219,6 +3339,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031915</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3329,6 +3454,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115036955</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3431,6 +3561,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510857</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3565,6 +3700,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115955282</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3667,6 +3807,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031911</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3769,6 +3914,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031912</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3866,6 +4016,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115510866</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3973,6 +4128,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115955366</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4097,6 +4257,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115955386</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4194,6 +4359,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031936</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4291,6 +4461,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031937</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4388,6 +4563,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031938</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4485,6 +4665,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031939</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4601,6 +4786,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115532590</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4702,6 +4892,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115265361</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4803,6 +4998,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115265442</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4910,6 +5110,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115958173</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5017,6 +5222,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115958869</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5114,6 +5324,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031932</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5211,6 +5426,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031933</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5313,6 +5533,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115265315</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5420,6 +5645,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115956400</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5522,6 +5752,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031929</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5627,6 +5862,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115265406</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5724,6 +5964,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031913</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5829,6 +6074,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123536289</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5934,6 +6184,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123536435</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6039,6 +6294,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123536478</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6146,6 +6406,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115956782</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6253,6 +6518,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115957098</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6350,6 +6620,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031923</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6447,6 +6722,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031926</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6554,6 +6834,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115957068</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6651,6 +6936,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031928</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6752,6 +7042,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115265362</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6853,6 +7148,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115265437</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6966,6 +7266,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115265369</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7076,6 +7381,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031917</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7188,6 +7498,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115958200</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7285,8 +7600,78 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116031940</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>